--- a/output/full_scan/batch_seq0_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq0_2026-08-28.xlsx
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1085.088869086127</v>
+        <v>1045.088869086127</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>372</v>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>944.2475185324216</v>
+        <v>904.2475185324216</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>543</v>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8085</v>
+        <v>8996</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>857.9689800774532</v>
+        <v>851.421088514585</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.1</v>
+        <v>1265</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>84.63222051783561</v>
+        <v>57.52808934387113</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.99178738926721</v>
+        <v>20.03952530203406</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.396898007745326</v>
+        <v>1.214122885108902</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4936552274678906</v>
+        <v>19.33770030040353</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8996</v>
+        <v>8103</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>851.421088514585</v>
+        <v>838.9012676051879</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1265</v>
+        <v>108.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.52808934387113</v>
+        <v>69.91476719590862</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>20.03952530203406</v>
+        <v>35.55848533529315</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.214122885108902</v>
+        <v>1.490126760518786</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>19.33770030040353</v>
+        <v>3.813647597143423</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8103</v>
+        <v>8085</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>838.9012676051879</v>
+        <v>837.9689800774532</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>108.5</v>
+        <v>16.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.91476719590862</v>
+        <v>84.63222051783561</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>35.55848533529315</v>
+        <v>26.99178738926721</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.490126760518786</v>
+        <v>2.396898007745326</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,11 +835,11 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.813647597143423</v>
+        <v>0.4936552274678906</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8074</v>
+        <v>8046</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>788.996530989212</v>
+        <v>758.9153955472511</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>58.1</v>
+        <v>1240</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.16775907572195</v>
+        <v>55.73210988771158</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>17.33245807020727</v>
+        <v>11.78438987634739</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.413264476834187</v>
+        <v>1.592991196433251</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.7033614105840116</v>
+        <v>3.498344395317822</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8093</v>
+        <v>8074</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>771.7975610993019</v>
+        <v>748.996530989212</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>27.45</v>
+        <v>58.1</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>60.15470585948914</v>
+        <v>55.16775907572195</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.53726308897875</v>
+        <v>17.33245807020727</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6814850529811827</v>
+        <v>2.413264476834187</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3625755108055706</v>
+        <v>0.7033614105840116</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8046</v>
+        <v>8093</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>758.9153955472511</v>
+        <v>731.7975610993019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1240</v>
+        <v>27.45</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.73210988771158</v>
+        <v>60.15470585948914</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>11.78438987634739</v>
+        <v>17.53726308897875</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.592991196433251</v>
+        <v>0.6814850529811827</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>3.498344395317822</v>
+        <v>0.3625755108055706</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8438</v>
+        <v>8431</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>660.7182400843329</v>
+        <v>661.0785313418255</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.05636561351042</v>
+        <v>61.35321731238828</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>19.16796702302545</v>
+        <v>12.78947214260705</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6817942862429923</v>
+        <v>4.619417750599464</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.491753040053128</v>
+        <v>0.4177484759829468</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8043</v>
+        <v>8438</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>648.3972715302924</v>
+        <v>660.7182400843329</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>148</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>53.65089235353283</v>
+        <v>57.05636561351042</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>16.07077391864188</v>
+        <v>19.16796702302545</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.746884954534204</v>
+        <v>0.6817942862429923</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.347158887388742</v>
+        <v>1.491753040053128</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1216,21 +1216,21 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8431</v>
+        <v>8163</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>631.0785313418255</v>
+        <v>630.1899425096074</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>52.1</v>
+        <v>31.85</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.35321731238828</v>
+        <v>47.86797462751906</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>12.78947214260705</v>
+        <v>18.20527838222707</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4.619417750599464</v>
+        <v>1.134116973862021</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.4177484759829468</v>
+        <v>0.2790347703430542</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8163</v>
+        <v>9905</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>630.1899425096074</v>
+        <v>612.5475081011043</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>31.85</v>
+        <v>21.55</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>47.86797462751906</v>
+        <v>62.51330083739982</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.20527838222707</v>
+        <v>19.16071977752667</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.134116973862021</v>
+        <v>0.4066977311998175</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2790347703430542</v>
+        <v>0.0042396631098939</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>9905</v>
+        <v>8043</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>612.5475081011043</v>
+        <v>608.3972715302924</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>21.55</v>
+        <v>148</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>62.51330083739982</v>
+        <v>53.65089235353283</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.16071977752667</v>
+        <v>16.07077391864188</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4066977311998175</v>
+        <v>2.746884954534204</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,11 +1365,11 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0042396631098939</v>
+        <v>1.347158887388742</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8182</v>
+        <v>8162</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>604.0462554558868</v>
+        <v>589.3127000082962</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>40.8</v>
+        <v>63.6</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>49.38768626939843</v>
+        <v>55.57875150639995</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>9.990273185424403</v>
+        <v>20.77640660170993</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6879295680513396</v>
+        <v>0.8984891942847006</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3585086662218606</v>
+        <v>1.375310038587649</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8171</v>
+        <v>8473</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>597.9149519241952</v>
+        <v>577.3999428877128</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>20.2</v>
+        <v>45.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>53.53741288264465</v>
+        <v>56.23627089135787</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>12.47092433857595</v>
+        <v>23.71869675197747</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.988736920900388</v>
+        <v>0.4805786213906571</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1150981116203288</v>
+        <v>0.3334525906450445</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8096</v>
+        <v>8105</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>596.8837548246106</v>
+        <v>568.6335036719528</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>109.5</v>
+        <v>16.65</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>39.94030076258591</v>
+        <v>49.37146710262267</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>23.37032343907727</v>
+        <v>26.20903331160673</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4204765651990727</v>
+        <v>1.300118002100555</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0567501473772225</v>
+        <v>0.0607076064525921</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8162</v>
+        <v>8182</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>589.3127000082962</v>
+        <v>564.0462554558868</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>63.6</v>
+        <v>40.8</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.57875150639995</v>
+        <v>49.38768626939843</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.77640660170993</v>
+        <v>9.990273185424403</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8984891942847006</v>
+        <v>0.6879295680513396</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.375310038587649</v>
+        <v>0.3585086662218606</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8299</v>
+        <v>8171</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>585.4855050612312</v>
+        <v>557.9149519241952</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2150</v>
+        <v>20.2</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.21489730837098</v>
+        <v>53.53741288264465</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12.88280869213377</v>
+        <v>12.47092433857595</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.6107085183462225</v>
+        <v>1.988736920900388</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>18.89783256620936</v>
+        <v>0.1150981116203288</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8473</v>
+        <v>8096</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>577.3999428877128</v>
+        <v>556.8837548246106</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45.9</v>
+        <v>109.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.23627089135787</v>
+        <v>39.94030076258591</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.71869675197747</v>
+        <v>23.37032343907727</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4805786213906571</v>
+        <v>0.4204765651990727</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.3334525906450445</v>
+        <v>0.0567501473772225</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8105</v>
+        <v>8213</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>568.6335036719528</v>
+        <v>548.4230835238865</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16.65</v>
+        <v>33.15</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>49.37146710262267</v>
+        <v>55.04290619050843</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>26.20903331160673</v>
+        <v>21.64270384834133</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.300118002100555</v>
+        <v>0.4982034334433036</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0607076064525921</v>
+        <v>0.1921620229995652</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8054</v>
+        <v>8299</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>567.5748186979937</v>
+        <v>545.4855050612312</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>84.59999999999999</v>
+        <v>2150</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>48.46601188566716</v>
+        <v>56.21489730837098</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.02637179235576</v>
+        <v>12.88280869213377</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.020330511386711</v>
+        <v>0.6107085183462225</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.102735546597222</v>
+        <v>18.89783256620936</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8213</v>
+        <v>8150</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>548.4230835238865</v>
+        <v>543.1502123250411</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>33.15</v>
+        <v>90.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.04290619050843</v>
+        <v>49.9917632878647</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>21.64270384834133</v>
+        <v>10.34543583735076</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4982034334433036</v>
+        <v>0.5983013912003253</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1921620229995652</v>
+        <v>0.6169288035503346</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8150</v>
+        <v>8054</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>543.1502123250411</v>
+        <v>527.5748186979936</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>90.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>49.9917632878647</v>
+        <v>48.46601188566716</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>10.34543583735076</v>
+        <v>18.02637179235576</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5983013912003253</v>
+        <v>1.020330511386711</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,11 +1948,11 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.6169288035503346</v>
+        <v>1.102735546597222</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8442</v>
+        <v>8064</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>487.6371978548239</v>
+        <v>493.3398046618004</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45.3</v>
+        <v>103</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.30612159198272</v>
+        <v>47.48967361192824</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.87773556228363</v>
+        <v>17.53616990013974</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.723812160854612</v>
+        <v>1.07527190368791</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0915695494535148</v>
+        <v>1.453348279213919</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8462</v>
+        <v>8442</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>486.6533952330282</v>
+        <v>487.6371978548239</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>171</v>
+        <v>45.3</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>52.5989882447574</v>
+        <v>50.30612159198272</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>40.81946624218929</v>
+        <v>21.87773556228363</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.186111142098068</v>
+        <v>0.723812160854612</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-1.049604073904097</v>
+        <v>0.0915695494535148</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>9955</v>
+        <v>8462</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>476.8601329498017</v>
+        <v>486.6533952330282</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>24.85</v>
+        <v>171</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.11177679053124</v>
+        <v>52.5989882447574</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>21.59338245229573</v>
+        <v>40.81946624218929</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4575495920001352</v>
+        <v>1.186111142098068</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1248857149787443</v>
+        <v>-1.049604073904097</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>9930</v>
+        <v>9955</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>476.1365268176141</v>
+        <v>476.8601329498017</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>63.1</v>
+        <v>24.85</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.13909481431705</v>
+        <v>52.11177679053124</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>29.72151659261095</v>
+        <v>21.59338245229573</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7117949515836881</v>
+        <v>0.4575495920001352</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1435948353175619</v>
+        <v>0.1248857149787443</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8070</v>
+        <v>9930</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>475.8057748154141</v>
+        <v>476.1365268176141</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>51.4</v>
+        <v>63.1</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>55.63552355757272</v>
+        <v>46.13909481431705</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.01476940521686</v>
+        <v>29.72151659261095</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.235259528115791</v>
+        <v>0.7117949515836881</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.337763642826882</v>
+        <v>0.1435948353175619</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8440</v>
+        <v>8070</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>472.7281794917795</v>
+        <v>475.8057748154141</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>20.55</v>
+        <v>51.4</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.78912460366707</v>
+        <v>55.63552355757272</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.43479933477428</v>
+        <v>17.01476940521686</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6299485194756417</v>
+        <v>1.235259528115791</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.1289581096082066</v>
+        <v>0.337763642826882</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8064</v>
+        <v>8092</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>463.3398046618004</v>
+        <v>462.4600554495257</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>103</v>
+        <v>13.15</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>47.48967361192824</v>
+        <v>48.5410684939558</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17.53616990013974</v>
+        <v>20.72082343695206</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.07527190368791</v>
+        <v>0.7585742031113174</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.453348279213919</v>
+        <v>0.1345603480737887</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8086</v>
+        <v>8227</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>458.5101973463186</v>
+        <v>443.2037116460196</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>117.5</v>
+        <v>161</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>48.36628197980028</v>
+        <v>52.86297982806222</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>22.4258972525593</v>
+        <v>18.36030476132764</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.7491937018888551</v>
+        <v>0.645877602091546</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.100350583472466</v>
+        <v>2.506703657953915</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8071</v>
+        <v>9136</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>455.6822717791341</v>
+        <v>435.2655196967184</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>24.5</v>
+        <v>11.7</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.22463474091749</v>
+        <v>51.37143003499804</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>14.42308677430792</v>
+        <v>10.40744770423163</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5322419513436029</v>
+        <v>0.6693593677246215</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1856795159377095</v>
+        <v>0.0679912262908187</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>9136</v>
+        <v>8440</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>435.2655196967184</v>
+        <v>432.7281794917795</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>11.7</v>
+        <v>20.55</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.37143003499804</v>
+        <v>55.78912460366707</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>10.40744770423163</v>
+        <v>22.43479933477428</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6693593677246215</v>
+        <v>0.6299485194756417</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0679912262908187</v>
+        <v>0.1289581096082066</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8092</v>
+        <v>8249</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>432.4600554495257</v>
+        <v>432.3826953639392</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>13.15</v>
+        <v>41.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>48.5410684939558</v>
+        <v>46.2910018417936</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20.72082343695206</v>
+        <v>23.71501130797508</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.7585742031113174</v>
+        <v>0.9466464428856448</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1345603480737887</v>
+        <v>0.2781614468480149</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8249</v>
+        <v>8102</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>432.3826953639392</v>
+        <v>430.227982492739</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>41.5</v>
+        <v>67.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>46.2910018417936</v>
+        <v>51.05330926162896</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.71501130797508</v>
+        <v>10.4038486796061</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9466464428856448</v>
+        <v>0.1226622035269554</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2781614468480149</v>
+        <v>0.2801587225198463</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8147</v>
+        <v>8222</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>431.7972607066613</v>
+        <v>425.376147793611</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>124</v>
+        <v>38.9</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>48.19304635130526</v>
+        <v>49.64461748480106</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.68951432347602</v>
+        <v>25.63351840447356</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.7774721687999316</v>
+        <v>1.391836561260074</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.093632752530516</v>
+        <v>0.0364400409835675</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8102</v>
+        <v>8429</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>430.227982492739</v>
+        <v>424.4985536354096</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>67.5</v>
+        <v>6.01</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.05330926162896</v>
+        <v>43.27957609638885</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>10.4038486796061</v>
+        <v>9.459947474331443</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.1226622035269554</v>
+        <v>0.6421301603580336</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.2801587225198463</v>
+        <v>0.01005847861335</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8222</v>
+        <v>8443</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>425.376147793611</v>
+        <v>421.1337850299653</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>38.9</v>
+        <v>11.25</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.64461748480106</v>
+        <v>36.38465672389037</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>25.63351840447356</v>
+        <v>41.75530419497464</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.391836561260074</v>
+        <v>0.287015252781813</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0364400409835675</v>
+        <v>-0.0159558632793368</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8429</v>
+        <v>8404</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>424.4985536354096</v>
+        <v>420.1231988233738</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>6.01</v>
+        <v>16.25</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.27957609638885</v>
+        <v>46.75043950329373</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>9.459947474331443</v>
+        <v>14.2252462686461</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6421301603580336</v>
+        <v>0.6738937089338222</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.01005847861335</v>
+        <v>0.0388955212881736</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8443</v>
+        <v>8482</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>421.1337850299653</v>
+        <v>419.2008383893084</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>11.25</v>
+        <v>47.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>36.38465672389037</v>
+        <v>50.22026919423537</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>41.75530419497464</v>
+        <v>3.851041046552351</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.287015252781813</v>
+        <v>1.358213258251903</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0159558632793368</v>
+        <v>-0.0050672804412945</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8404</v>
+        <v>8086</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>420.1231988233738</v>
+        <v>418.5101973463186</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>16.25</v>
+        <v>117.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>46.75043950329373</v>
+        <v>48.36628197980028</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>14.2252462686461</v>
+        <v>22.4258972525593</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6738937089338222</v>
+        <v>0.7491937018888551</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0388955212881736</v>
+        <v>1.100350583472466</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8482</v>
+        <v>8240</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>419.2008383893084</v>
+        <v>416.0376455055229</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>47.7</v>
+        <v>44.8</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.22026919423537</v>
+        <v>54.89506144442905</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3.851041046552351</v>
+        <v>25.74598094227343</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.358213258251903</v>
+        <v>1.594371110257083</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0050672804412945</v>
+        <v>0.7145045700152585</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8240</v>
+        <v>8071</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>416.0376455055229</v>
+        <v>415.6822717791341</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>44.8</v>
+        <v>24.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.89506144442905</v>
+        <v>52.22463474091749</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.74598094227343</v>
+        <v>14.42308677430792</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.594371110257083</v>
+        <v>0.5322419513436029</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.7145045700152585</v>
+        <v>0.1856795159377095</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8227</v>
+        <v>9105</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>413.2037116460196</v>
+        <v>412.90479348002</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>161</v>
+        <v>8.35</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.86297982806222</v>
+        <v>48.40698646996236</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.36030476132764</v>
+        <v>15.48584847781395</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.645877602091546</v>
+        <v>0.6302401116078229</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>2.506703657953915</v>
+        <v>0.0164873452807053</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>9105</v>
+        <v>8261</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>412.90479348002</v>
+        <v>411.9116592553011</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>8.35</v>
+        <v>187.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.40698646996236</v>
+        <v>46.56438437109063</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.48584847781395</v>
+        <v>16.50361183090706</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6302401116078229</v>
+        <v>1.416550959432189</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0164873452807053</v>
+        <v>2.695340153736435</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8121</v>
+        <v>8464</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>412.5757739810189</v>
+        <v>410.9134912014217</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>28.55</v>
+        <v>366.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40.97527282601633</v>
+        <v>47.02551196520062</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.92004620778427</v>
+        <v>20.91498724169968</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.8004529196264965</v>
+        <v>0.7882694408721826</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.4282836220086352</v>
+        <v>-1.799318302168852</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8261</v>
+        <v>8111</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>411.9116592553011</v>
+        <v>401.9214231703433</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>187.5</v>
+        <v>62.4</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.56438437109063</v>
+        <v>54.82189044109823</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>16.50361183090706</v>
+        <v>19.5454476004508</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.416550959432189</v>
+        <v>0.6118522106575103</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.695340153736435</v>
+        <v>0.3985204273748053</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8464</v>
+        <v>8045</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>410.9134912014217</v>
+        <v>400.150450413107</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>366.5</v>
+        <v>53.2</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.02551196520062</v>
+        <v>47.28582705519808</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.91498724169968</v>
+        <v>14.09958840750623</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7882694408721826</v>
+        <v>0.7385276413410768</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-1.799318302168852</v>
+        <v>0.350037499707398</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8109</v>
+        <v>8104</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>407.8338964789809</v>
+        <v>392.9330110216501</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>130.5</v>
+        <v>31.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.68517557751379</v>
+        <v>46.00945694864662</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>16.96619817811739</v>
+        <v>25.38397362058426</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4810904473676982</v>
+        <v>0.9073785179289372</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0194607667351514</v>
+        <v>0.3117951838562334</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8045</v>
+        <v>8499</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>400.150450413107</v>
+        <v>392.6084857295309</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>53.2</v>
+        <v>271</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>47.28582705519808</v>
+        <v>51.64695815460291</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.09958840750623</v>
+        <v>14.92291162693559</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7385276413410768</v>
+        <v>3.836917441150533</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.350037499707398</v>
+        <v>2.745386235093792</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, dealer_buy_3d</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8104</v>
+        <v>8147</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>392.9330110216501</v>
+        <v>391.7972607066613</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>31.5</v>
+        <v>124</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.00945694864662</v>
+        <v>48.19304635130526</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.38397362058426</v>
+        <v>25.68951432347602</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9073785179289372</v>
+        <v>0.7774721687999316</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.3117951838562334</v>
+        <v>1.093632752530516</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8499</v>
+        <v>8422</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>392.6084857295309</v>
+        <v>389.7602426735865</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>271</v>
+        <v>27.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.64695815460291</v>
+        <v>54.27055549046003</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.92291162693559</v>
+        <v>13.56952754164086</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.836917441150533</v>
+        <v>0.8474869936781482</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.745386235093792</v>
+        <v>0.08745561097681021</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8422</v>
+        <v>8080</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>389.7602426735865</v>
+        <v>373.9083738510026</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>54.27055549046003</v>
+        <v>51.45673140752194</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>13.56952754164086</v>
+        <v>52.76560954830051</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8474869936781482</v>
+        <v>0.8125609596685804</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.08745561097681021</v>
+        <v>0.0123244625743637</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8932</v>
+        <v>8121</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>385.1700503905222</v>
+        <v>372.5757739810189</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>94.3</v>
+        <v>28.55</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.30117549667552</v>
+        <v>40.97527282601633</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.49952938915958</v>
+        <v>28.92004620778427</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.261922218506764</v>
+        <v>0.8004529196264965</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.4219506902806326</v>
+        <v>0.4282836220086352</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8111</v>
+        <v>8926</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>371.9214231703433</v>
+        <v>369.2418346005444</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>62.4</v>
+        <v>56.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>54.82189044109823</v>
+        <v>38.69312547858893</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.5454476004508</v>
+        <v>30.932238668155</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6118522106575103</v>
+        <v>0.5788568813467081</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3985204273748053</v>
+        <v>0.4482227638970291</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8926</v>
+        <v>8110</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>369.2418346005444</v>
+        <v>368.1980553713538</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>56.8</v>
+        <v>46</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>38.69312547858893</v>
+        <v>51.99175645829633</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>30.932238668155</v>
+        <v>9.866228651315454</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5788568813467081</v>
+        <v>0.7061173702573003</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.4482227638970291</v>
+        <v>0.3696494334897452</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8110</v>
+        <v>8109</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>368.1980553713538</v>
+        <v>367.8338964789809</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46</v>
+        <v>130.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.99175645829633</v>
+        <v>50.68517557751379</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>9.866228651315454</v>
+        <v>16.96619817811739</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7061173702573003</v>
+        <v>0.4810904473676982</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.3696494334897452</v>
+        <v>-0.0194607667351514</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8289</v>
+        <v>8481</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>365.0631138939091</v>
+        <v>361.839347880324</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>46.35</v>
+        <v>41.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>48.245697573123</v>
+        <v>55.31009880712149</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.52721976460336</v>
+        <v>12.33478475097821</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6784298967188122</v>
+        <v>0.197371018039711</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.5729448057913278</v>
+        <v>0.1034232606627103</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8481</v>
+        <v>8201</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>361.839347880324</v>
+        <v>353.0538644423702</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>41.2</v>
+        <v>11.9</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>55.31009880712149</v>
+        <v>47.77143866879237</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.33478475097821</v>
+        <v>20.12012989206895</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.197371018039711</v>
+        <v>1.299892304013377</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1034232606627103</v>
+        <v>0.047371507072039</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8201</v>
+        <v>8112</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>353.0538644423702</v>
+        <v>349.435183287089</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>11.9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.77143866879237</v>
+        <v>49.66301948034295</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>20.12012989206895</v>
+        <v>12.2758749058418</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.299892304013377</v>
+        <v>0.47216085184195</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.047371507072039</v>
+        <v>-0.2637958166129341</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8234</v>
+        <v>8374</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>352.248164047337</v>
+        <v>346.0726461865015</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>68</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.68276879771057</v>
+        <v>49.97851672376336</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.76092435233267</v>
+        <v>16.36838679175931</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5116699498884609</v>
+        <v>0.4595371343834503</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0783693473267721</v>
+        <v>0.0590849115448964</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8112</v>
+        <v>8081</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>349.435183287089</v>
+        <v>345.8567585178446</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>260</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.66301948034295</v>
+        <v>49.63794525201446</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.2758749058418</v>
+        <v>16.31761830309232</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.47216085184195</v>
+        <v>0.5485051840332292</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.2637958166129341</v>
+        <v>1.070209476859329</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8374</v>
+        <v>8932</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>346.0726461865015</v>
+        <v>345.1700503905222</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.97851672376336</v>
+        <v>39.30117549667552</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.36838679175931</v>
+        <v>13.49952938915958</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4595371343834503</v>
+        <v>2.261922218506764</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0590849115448964</v>
+        <v>-0.4219506902806326</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8081</v>
+        <v>8289</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>345.8567585178446</v>
+        <v>325.0631138939091</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>260</v>
+        <v>46.35</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.63794525201446</v>
+        <v>48.245697573123</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.31761830309232</v>
+        <v>18.52721976460336</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5485051840332292</v>
+        <v>0.6784298967188122</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.070209476859329</v>
+        <v>0.5729448057913278</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8080</v>
+        <v>8476</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>343.9083738510026</v>
+        <v>322.6258853570554</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>28</v>
+        <v>19.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>51.45673140752194</v>
+        <v>43.00597295849971</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>52.76560954830051</v>
+        <v>11.63199103327738</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8125609596685804</v>
+        <v>0.7474903649016681</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0123244625743637</v>
+        <v>0.0479267900447863</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8183</v>
+        <v>9110</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>338.8548965242758</v>
+        <v>319.7758844017502</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>29.65</v>
+        <v>3.1</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.24330969818532</v>
+        <v>51.73005889180092</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.3903446200394</v>
+        <v>6.64990059568474</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7992490291360574</v>
+        <v>0.506490107966808</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.08415852397757501</v>
+        <v>0.0830707191162364</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8476</v>
+        <v>8101</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>322.6258853570554</v>
+        <v>316.6453511539835</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>19.9</v>
+        <v>12.4</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.00597295849971</v>
+        <v>51.12102104606424</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>11.63199103327738</v>
+        <v>8.944199604548988</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7474903649016681</v>
+        <v>0.2645351153983523</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0479267900447863</v>
+        <v>0.3246304680695999</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>9110</v>
+        <v>8234</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>319.7758844017502</v>
+        <v>312.248164047337</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>3.1</v>
+        <v>68</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.73005889180092</v>
+        <v>51.68276879771057</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6.64990059568474</v>
+        <v>18.76092435233267</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.506490107966808</v>
+        <v>0.5116699498884609</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0830707191162364</v>
+        <v>-0.0783693473267721</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8076</v>
+        <v>8463</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>318.8989948003961</v>
+        <v>310.933107809466</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>23.25</v>
+        <v>21.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45.4766614622364</v>
+        <v>56.72291130560987</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7.765705764801571</v>
+        <v>17.65272109793246</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.927242813316114</v>
+        <v>0.5005092302243873</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0557769420176847</v>
+        <v>0.0587176485514415</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8101</v>
+        <v>8183</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>316.6453511539835</v>
+        <v>298.8548965242758</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.4</v>
+        <v>29.65</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.12102104606424</v>
+        <v>48.24330969818532</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.944199604548988</v>
+        <v>20.3903446200394</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.2645351153983523</v>
+        <v>0.7992490291360574</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.3246304680695999</v>
+        <v>0.08415852397757501</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8463</v>
+        <v>9902</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>310.933107809466</v>
+        <v>298.6357290999228</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>21.5</v>
+        <v>13.6</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>56.72291130560987</v>
+        <v>44.93355995671451</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.65272109793246</v>
+        <v>8.800649991244546</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5005092302243873</v>
+        <v>1.057646849347029</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,11 +4545,11 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0587176485514415</v>
+        <v>-0.0077146164293841</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>307.1779526627139</v>
+        <v>287.1779526627139</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>24.45</v>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>9902</v>
+        <v>8410</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>298.6357290999228</v>
+        <v>286.6167334714953</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>13.6</v>
+        <v>30.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.93355995671451</v>
+        <v>38.21061797999595</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>8.800649991244546</v>
+        <v>22.26521169237453</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.057646849347029</v>
+        <v>0.2382106871551852</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0077146164293841</v>
+        <v>-0.0996335084966169</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8390</v>
+        <v>9802</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>298.1311432627424</v>
+        <v>282.7894927760062</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>99.8</v>
+        <v>71.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.94684347569449</v>
+        <v>47.60562640678203</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.73638214460221</v>
+        <v>10.69112895582835</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7733986005243871</v>
+        <v>0.4038462947789248</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.5920776195074637</v>
+        <v>0.2003637249161394</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>9802</v>
+        <v>8076</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>282.7894927760062</v>
+        <v>278.8989948003961</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>71.7</v>
+        <v>23.25</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.60562640678203</v>
+        <v>45.4766614622364</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.69112895582835</v>
+        <v>7.765705764801571</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4038462947789248</v>
+        <v>0.927242813316114</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2003637249161394</v>
+        <v>0.0557769420176847</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8068</v>
+        <v>9103</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>280.4484834846212</v>
+        <v>269.9440760791496</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>17.05</v>
+        <v>5.08</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.67537544332563</v>
+        <v>43.7771468684176</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.51912143066086</v>
+        <v>11.0537142644062</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7394331220603636</v>
+        <v>0.5295855790457407</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0110821713740467</v>
+        <v>-0.009073246204712899</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>9103</v>
+        <v>8131</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>269.9440760791496</v>
+        <v>269.2006614636685</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>5.08</v>
+        <v>62.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.7771468684176</v>
+        <v>46.97646623456652</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.0537142644062</v>
+        <v>7.419433536762348</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5295855790457407</v>
+        <v>0.6079335757405125</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.009073246204712899</v>
+        <v>0.2923608855500188</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8131</v>
+        <v>9904</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>269.2006614636685</v>
+        <v>264.5091039913911</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>62.7</v>
+        <v>24.35</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.97646623456652</v>
+        <v>45.99115236267824</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7.419433536762348</v>
+        <v>19.42101884805333</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6079335757405125</v>
+        <v>1.205746144177928</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.2923608855500188</v>
+        <v>0.0431915152399065</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8059</v>
+        <v>8488</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>264.8325375032354</v>
+        <v>261.9280881202661</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>13.9</v>
+        <v>10</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.20819473006895</v>
+        <v>50.91179291380178</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>19.7836643834587</v>
+        <v>18.21949275833072</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9932307280114778</v>
+        <v>0.1362363350090402</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.08240648068041979</v>
+        <v>-0.0121638534925729</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>9904</v>
+        <v>8411</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>264.5091039913911</v>
+        <v>260.0967947516219</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>24.35</v>
+        <v>12.95</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.99115236267824</v>
+        <v>53.38115655379207</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.42101884805333</v>
+        <v>14.46462542383209</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.205746144177928</v>
+        <v>0.3031618294869521</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0431915152399065</v>
+        <v>-0.0263317978628087</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8050</v>
+        <v>8341</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>263.2064813631319</v>
+        <v>259.2567896561655</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>56.4</v>
+        <v>76.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>44.62307351138001</v>
+        <v>52.83350096299573</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.22999421900934</v>
+        <v>11.7411269595829</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.2693961994881253</v>
+        <v>1.084434984215798</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.379537054337907</v>
+        <v>0.0910451440759828</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8488</v>
+        <v>8390</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>261.9280881202661</v>
+        <v>258.1311432627424</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>10</v>
+        <v>99.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>50.91179291380178</v>
+        <v>51.94684347569449</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.21949275833072</v>
+        <v>15.73638214460221</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.1362363350090402</v>
+        <v>0.7733986005243871</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0121638534925729</v>
+        <v>0.5920776195074637</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8097</v>
+        <v>8454</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>260.9683503068344</v>
+        <v>253.400789770245</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>49.05</v>
+        <v>250</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>28.94172809166362</v>
+        <v>42.29666094501501</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>25.41906707033725</v>
+        <v>11.43662052837788</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.036581317635603</v>
+        <v>0.4960576983614056</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0188658313818725</v>
+        <v>-0.3220331939957894</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8411</v>
+        <v>8477</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>260.0967947516219</v>
+        <v>249.6137774489242</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>12.95</v>
+        <v>15.45</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>53.38115655379207</v>
+        <v>49.14544229135476</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.46462542383209</v>
+        <v>4.744129656839474</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3031618294869521</v>
+        <v>0.3002377327243102</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0263317978628087</v>
+        <v>-0.0205846582288395</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8341</v>
+        <v>8114</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>259.2567896561655</v>
+        <v>245.9465628958777</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>76.7</v>
+        <v>195</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>52.83350096299573</v>
+        <v>41.78842576348874</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>11.7411269595829</v>
+        <v>14.73003628992774</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.084434984215798</v>
+        <v>0.4187019805029252</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0910451440759828</v>
+        <v>-1.469599321471017</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8410</v>
+        <v>8068</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>256.6167334714953</v>
+        <v>240.4484834846212</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>30.5</v>
+        <v>17.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.21061797999595</v>
+        <v>40.67537544332563</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.26521169237453</v>
+        <v>13.51912143066086</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2382106871551852</v>
+        <v>0.7394331220603636</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0996335084966169</v>
+        <v>0.0110821713740467</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8091</v>
+        <v>8940</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>255.2157753916384</v>
+        <v>237.1034079700872</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>220.5</v>
+        <v>15.15</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.81658541889351</v>
+        <v>38.52797774303279</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14.9075951421026</v>
+        <v>13.62035520824137</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5736643339597504</v>
+        <v>1.975245236505572</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.4703012776364677</v>
+        <v>0.0230952928464726</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8454</v>
+        <v>8059</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>253.400789770245</v>
+        <v>224.8325375032355</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>250</v>
+        <v>13.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.29666094501501</v>
+        <v>42.20819473006895</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>11.43662052837788</v>
+        <v>19.7836643834587</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4960576983614056</v>
+        <v>0.9932307280114778</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.3220331939957894</v>
+        <v>0.08240648068041979</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8383</v>
+        <v>8050</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>251.7646311256282</v>
+        <v>223.206481363132</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.70365551214903</v>
+        <v>44.62307351138001</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>13.28128710190597</v>
+        <v>11.22999421900934</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8377401413742578</v>
+        <v>0.2693961994881253</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3045867920248422</v>
+        <v>-0.379537054337907</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8477</v>
+        <v>8097</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>249.6137774489242</v>
+        <v>220.9683503068344</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15.45</v>
+        <v>49.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.14544229135476</v>
+        <v>28.94172809166362</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>4.744129656839474</v>
+        <v>25.41906707033725</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3002377327243102</v>
+        <v>1.036581317635603</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0205846582288395</v>
+        <v>0.0188658313818725</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8114</v>
+        <v>8091</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>245.9465628958777</v>
+        <v>215.2157753916384</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>195</v>
+        <v>220.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>41.78842576348874</v>
+        <v>43.81658541889351</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.73003628992774</v>
+        <v>14.9075951421026</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4187019805029252</v>
+        <v>0.5736643339597504</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-1.469599321471017</v>
+        <v>0.4703012776364677</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8423</v>
+        <v>8383</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>239.5294219576645</v>
+        <v>211.7646311256282</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>17.8</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>49.46531288669466</v>
+        <v>44.70365551214903</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.29879418738548</v>
+        <v>13.28128710190597</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.168418916176172</v>
+        <v>0.8377401413742578</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0046179929742114</v>
+        <v>-0.3045867920248422</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8940</v>
+        <v>8044</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>237.1034079700872</v>
+        <v>208.2268261383359</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>15.15</v>
+        <v>24.4</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>38.52797774303279</v>
+        <v>33.4652350316892</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13.62035520824137</v>
+        <v>14.73985542213635</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.975245236505572</v>
+        <v>0.9002424136611178</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0230952928464726</v>
+        <v>-0.1482343385507427</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8044</v>
+        <v>8455</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>228.2268261383359</v>
+        <v>203.8628032094371</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>33.4652350316892</v>
+        <v>10.89500362816788</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>14.73985542213635</v>
+        <v>15.25945261563091</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9002424136611178</v>
+        <v>0.0015481823371747</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.1482343385507427</v>
+        <v>-1.432531609260909</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8047</v>
+        <v>8423</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>227.6059744411997</v>
+        <v>199.5294219576645</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>44</v>
+        <v>17.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>43.51797461804424</v>
+        <v>49.46531288669466</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.436972780240485</v>
+        <v>17.29879418738548</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.2562781745818181</v>
+        <v>1.168418916176172</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.3590955117073157</v>
+        <v>-0.0046179929742114</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8455</v>
+        <v>8466</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>223.8628032094371</v>
+        <v>196.8753968565658</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>10.89500362816788</v>
+        <v>37.54733041050686</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.25945261563091</v>
+        <v>27.24543120498111</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.0015481823371747</v>
+        <v>1.019908712153769</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-1.432531609260909</v>
+        <v>-0.0471496589042342</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8088</v>
+        <v>8277</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.5882092332892</v>
+        <v>193.1984162231618</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45.75</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.85895515884366</v>
+        <v>48.9580764299736</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.58343758209626</v>
+        <v>9.826830787026475</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.380398839651127</v>
+        <v>1.392822576676382</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2289020006305362</v>
+        <v>0.0466351654388627</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8291</v>
+        <v>8047</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>206.6982773355024</v>
+        <v>187.6059744411997</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>35.75</v>
+        <v>44</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>47.55060562929813</v>
+        <v>43.51797461804424</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>12.30969215273276</v>
+        <v>9.436972780240485</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3571090489235667</v>
+        <v>0.2562781745818181</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1792838317826992</v>
+        <v>-0.3590955117073157</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8466</v>
+        <v>8072</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>196.8753968565658</v>
+        <v>178.5401385744399</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>15.5</v>
+        <v>26.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>37.54733041050686</v>
+        <v>43.46010786159694</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>27.24543120498111</v>
+        <v>19.04184195759062</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.019908712153769</v>
+        <v>1.200916113631522</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0471496589042342</v>
+        <v>0.059015407556645</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8072</v>
+        <v>8088</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>178.5401385744399</v>
+        <v>167.5882092332892</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>26.2</v>
+        <v>45.75</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.46010786159694</v>
+        <v>41.85895515884366</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>19.04184195759062</v>
+        <v>13.58343758209626</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.200916113631522</v>
+        <v>0.380398839651127</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.059015407556645</v>
+        <v>0.2289020006305362</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8472</v>
+        <v>8291</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>165.107154130495</v>
+        <v>166.6982773355024</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>65.7</v>
+        <v>35.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>33.99492092259649</v>
+        <v>47.55060562929813</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.22152591191638</v>
+        <v>12.30969215273276</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.117458716199917</v>
+        <v>0.3571090489235667</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0399684010048533</v>
+        <v>0.1792838317826992</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8087</v>
+        <v>8478</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>163.7995802187797</v>
+        <v>149.1209667446585</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>26.1</v>
+        <v>141.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>49.23366240885399</v>
+        <v>39.86605207119235</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7.442532682370188</v>
+        <v>12.34218468765116</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.0514857942112805</v>
+        <v>0.8449057976917083</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0461019516817143</v>
+        <v>0.1843121826923046</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8277</v>
+        <v>8069</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>163.1984162231618</v>
+        <v>146.5043459547673</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>160.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>48.9580764299736</v>
+        <v>38.06149222540301</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9.826830787026475</v>
+        <v>18.56615933442729</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.392822576676382</v>
+        <v>0.52749184463082</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0466351654388627</v>
+        <v>-0.0901316805148599</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8478</v>
+        <v>8067</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>149.1209667446585</v>
+        <v>145.4913764042074</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>141.5</v>
+        <v>12.3</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>39.86605207119235</v>
+        <v>42.81140658262501</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.34218468765116</v>
+        <v>8.236485481375427</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.8449057976917083</v>
+        <v>0.7491376404207429</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1843121826923046</v>
+        <v>-0.0709777697038179</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8067</v>
+        <v>8487</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>145.4913764042074</v>
+        <v>145.2077589963297</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>12.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>42.81140658262501</v>
+        <v>40.51912516072922</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.236485481375427</v>
+        <v>14.48270247015094</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.7491376404207429</v>
+        <v>0.4914339985632009</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0709777697038179</v>
+        <v>0.1680605367960981</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8487</v>
+        <v>8472</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>145.2077589963297</v>
+        <v>145.107154130495</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>40.51912516072922</v>
+        <v>33.99492092259649</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.48270247015094</v>
+        <v>17.22152591191638</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4914339985632009</v>
+        <v>1.117458716199917</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1680605367960981</v>
+        <v>0.0399684010048533</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8176</v>
+        <v>8087</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>137.866632728196</v>
+        <v>123.7995802187796</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>9.81</v>
+        <v>26.1</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.72309341176243</v>
+        <v>49.23366240885399</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.55065898907922</v>
+        <v>7.442532682370188</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.32393378350222</v>
+        <v>0.0514857942112805</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0116230971988206</v>
+        <v>0.0461019516817143</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8048</v>
+        <v>8089</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>134.7335334069331</v>
+        <v>121.6864438811206</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>51.8</v>
+        <v>17.95</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.11415786617395</v>
+        <v>44.06215656359527</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.64254169834261</v>
+        <v>8.355367319494835</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.5122234962924279</v>
+        <v>1.11229491846476</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.3108742476852033</v>
+        <v>0.0729190164303973</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8084</v>
+        <v>8176</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>131.1400459574824</v>
+        <v>97.86663272819597</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>46</v>
+        <v>9.81</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.83602645694072</v>
+        <v>43.72309341176243</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.98345528502759</v>
+        <v>17.55065898907922</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5140045957482413</v>
+        <v>0.32393378350222</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.4544806069317083</v>
+        <v>-0.0116230971988206</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8069</v>
+        <v>8048</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>116.5043459547673</v>
+        <v>94.73353340693316</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>160.5</v>
+        <v>51.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>38.06149222540301</v>
+        <v>43.11415786617395</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>18.56615933442729</v>
+        <v>13.64254169834261</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.52749184463082</v>
+        <v>0.5122234962924279</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0901316805148599</v>
+        <v>0.3108742476852033</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>8089</v>
+        <v>8084</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>91.6864438811206</v>
+        <v>91.1400459574824</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>17.95</v>
+        <v>46</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>44.06215656359527</v>
+        <v>44.83602645694072</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>8.355367319494835</v>
+        <v>17.98345528502759</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.11229491846476</v>
+        <v>0.5140045957482413</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0729190164303973</v>
+        <v>-0.4544806069317083</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq0_2026-08-28.xlsx
+++ b/output/full_scan/batch_seq0_2026-08-28.xlsx
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1045.088869086127</v>
+        <v>1085.088869086127</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>372</v>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>904.2475185324216</v>
+        <v>944.2475185324216</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>543</v>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8996</v>
+        <v>8085</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>851.421088514585</v>
+        <v>857.9689800774532</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1265</v>
+        <v>16.1</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>57.52808934387113</v>
+        <v>84.63222051783561</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.03952530203406</v>
+        <v>26.99178738926721</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.214122885108902</v>
+        <v>2.396898007745326</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>19.33770030040353</v>
+        <v>0.4936552274678906</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8103</v>
+        <v>8996</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>838.9012676051879</v>
+        <v>851.421088514585</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>108.5</v>
+        <v>1265</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>69.91476719590862</v>
+        <v>57.52808934387113</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>35.55848533529315</v>
+        <v>20.03952530203406</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.490126760518786</v>
+        <v>1.214122885108902</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.813647597143423</v>
+        <v>19.33770030040353</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8085</v>
+        <v>8103</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>837.9689800774532</v>
+        <v>838.9012676051879</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.1</v>
+        <v>108.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>84.63222051783561</v>
+        <v>69.91476719590862</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.99178738926721</v>
+        <v>35.55848533529315</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.396898007745326</v>
+        <v>1.490126760518786</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,11 +835,11 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4936552274678906</v>
+        <v>3.813647597143423</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -898,21 +898,21 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8046</v>
+        <v>8074</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>758.9153955472511</v>
+        <v>788.996530989212</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1240</v>
+        <v>58.1</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.73210988771158</v>
+        <v>55.16775907572195</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>11.78438987634739</v>
+        <v>17.33245807020727</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.592991196433251</v>
+        <v>2.413264476834187</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.498344395317822</v>
+        <v>0.7033614105840116</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8074</v>
+        <v>8093</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>748.996530989212</v>
+        <v>771.7975610993019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>58.1</v>
+        <v>27.45</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>55.16775907572195</v>
+        <v>60.15470585948914</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.33245807020727</v>
+        <v>17.53726308897875</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.413264476834187</v>
+        <v>0.6814850529811827</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.7033614105840116</v>
+        <v>0.3625755108055706</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8093</v>
+        <v>8046</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>731.7975610993019</v>
+        <v>758.9153955472511</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>27.45</v>
+        <v>1240</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.15470585948914</v>
+        <v>55.73210988771158</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>17.53726308897875</v>
+        <v>11.78438987634739</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6814850529811827</v>
+        <v>1.592991196433251</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.3625755108055706</v>
+        <v>3.498344395317822</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8431</v>
+        <v>8438</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>661.0785313418255</v>
+        <v>660.7182400843329</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>52.1</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.35321731238828</v>
+        <v>57.05636561351042</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>12.78947214260705</v>
+        <v>19.16796702302545</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>4.619417750599464</v>
+        <v>0.6817942862429923</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.4177484759829468</v>
+        <v>1.491753040053128</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8438</v>
+        <v>8043</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>660.7182400843329</v>
+        <v>648.3972715302924</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>148</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.05636561351042</v>
+        <v>53.65089235353283</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>19.16796702302545</v>
+        <v>16.07077391864188</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6817942862429923</v>
+        <v>2.746884954534204</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.491753040053128</v>
+        <v>1.347158887388742</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1216,21 +1216,21 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8163</v>
+        <v>8431</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>630.1899425096074</v>
+        <v>631.0785313418255</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>31.85</v>
+        <v>52.1</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>47.86797462751906</v>
+        <v>61.35321731238828</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>18.20527838222707</v>
+        <v>12.78947214260705</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.134116973862021</v>
+        <v>4.619417750599464</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2790347703430542</v>
+        <v>0.4177484759829468</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>9905</v>
+        <v>8163</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>612.5475081011043</v>
+        <v>630.1899425096074</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>21.55</v>
+        <v>31.85</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>62.51330083739982</v>
+        <v>47.86797462751906</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19.16071977752667</v>
+        <v>18.20527838222707</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4066977311998175</v>
+        <v>1.134116973862021</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0042396631098939</v>
+        <v>0.2790347703430542</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8043</v>
+        <v>9905</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>608.3972715302924</v>
+        <v>612.5475081011043</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>148</v>
+        <v>21.55</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.65089235353283</v>
+        <v>62.51330083739982</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>16.07077391864188</v>
+        <v>19.16071977752667</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.746884954534204</v>
+        <v>0.4066977311998175</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,11 +1365,11 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.347158887388742</v>
+        <v>0.0042396631098939</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8162</v>
+        <v>8182</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>589.3127000082962</v>
+        <v>604.0462554558868</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>63.6</v>
+        <v>40.8</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.57875150639995</v>
+        <v>49.38768626939843</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>20.77640660170993</v>
+        <v>9.990273185424403</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.8984891942847006</v>
+        <v>0.6879295680513396</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.375310038587649</v>
+        <v>0.3585086662218606</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8473</v>
+        <v>8171</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>577.3999428877128</v>
+        <v>597.9149519241952</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45.9</v>
+        <v>20.2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>56.23627089135787</v>
+        <v>53.53741288264465</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>23.71869675197747</v>
+        <v>12.47092433857595</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4805786213906571</v>
+        <v>1.988736920900388</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3334525906450445</v>
+        <v>0.1150981116203288</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8105</v>
+        <v>8096</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>568.6335036719528</v>
+        <v>596.8837548246106</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16.65</v>
+        <v>109.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>49.37146710262267</v>
+        <v>39.94030076258591</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.20903331160673</v>
+        <v>23.37032343907727</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.300118002100555</v>
+        <v>0.4204765651990727</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.0607076064525921</v>
+        <v>0.0567501473772225</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8182</v>
+        <v>8162</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>564.0462554558868</v>
+        <v>589.3127000082962</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>40.8</v>
+        <v>63.6</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.38768626939843</v>
+        <v>55.57875150639995</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>9.990273185424403</v>
+        <v>20.77640660170993</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6879295680513396</v>
+        <v>0.8984891942847006</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.3585086662218606</v>
+        <v>1.375310038587649</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8171</v>
+        <v>8299</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>557.9149519241952</v>
+        <v>585.4855050612312</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>20.2</v>
+        <v>2150</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.53741288264465</v>
+        <v>56.21489730837098</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>12.47092433857595</v>
+        <v>12.88280869213377</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.988736920900388</v>
+        <v>0.6107085183462225</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1150981116203288</v>
+        <v>18.89783256620936</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8096</v>
+        <v>8473</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>556.8837548246106</v>
+        <v>577.3999428877128</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>109.5</v>
+        <v>45.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>39.94030076258591</v>
+        <v>56.23627089135787</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.37032343907727</v>
+        <v>23.71869675197747</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4204765651990727</v>
+        <v>0.4805786213906571</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0567501473772225</v>
+        <v>0.3334525906450445</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8213</v>
+        <v>8105</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>548.4230835238865</v>
+        <v>568.6335036719528</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>33.15</v>
+        <v>16.65</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.04290619050843</v>
+        <v>49.37146710262267</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.64270384834133</v>
+        <v>26.20903331160673</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4982034334433036</v>
+        <v>1.300118002100555</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1921620229995652</v>
+        <v>0.0607076064525921</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8299</v>
+        <v>8054</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>545.4855050612312</v>
+        <v>567.5748186979937</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2150</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.21489730837098</v>
+        <v>48.46601188566716</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12.88280869213377</v>
+        <v>18.02637179235576</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6107085183462225</v>
+        <v>1.020330511386711</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>18.89783256620936</v>
+        <v>1.102735546597222</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8150</v>
+        <v>8213</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>543.1502123250411</v>
+        <v>548.4230835238865</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>90.5</v>
+        <v>33.15</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.9917632878647</v>
+        <v>55.04290619050843</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10.34543583735076</v>
+        <v>21.64270384834133</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5983013912003253</v>
+        <v>0.4982034334433036</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6169288035503346</v>
+        <v>0.1921620229995652</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8054</v>
+        <v>8150</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>527.5748186979936</v>
+        <v>543.1502123250411</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>84.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>48.46601188566716</v>
+        <v>49.9917632878647</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>18.02637179235576</v>
+        <v>10.34543583735076</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.020330511386711</v>
+        <v>0.5983013912003253</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,11 +1948,11 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.102735546597222</v>
+        <v>0.6169288035503346</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8064</v>
+        <v>8442</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>493.3398046618004</v>
+        <v>487.6371978548239</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>103</v>
+        <v>45.3</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>47.48967361192824</v>
+        <v>50.30612159198272</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>17.53616990013974</v>
+        <v>21.87773556228363</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.07527190368791</v>
+        <v>0.723812160854612</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.453348279213919</v>
+        <v>0.0915695494535148</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8442</v>
+        <v>8462</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>487.6371978548239</v>
+        <v>486.6533952330282</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45.3</v>
+        <v>171</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.30612159198272</v>
+        <v>52.5989882447574</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.87773556228363</v>
+        <v>40.81946624218929</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.723812160854612</v>
+        <v>1.186111142098068</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0915695494535148</v>
+        <v>-1.049604073904097</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8462</v>
+        <v>9955</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>486.6533952330282</v>
+        <v>476.8601329498017</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>171</v>
+        <v>24.85</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.5989882447574</v>
+        <v>52.11177679053124</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>40.81946624218929</v>
+        <v>21.59338245229573</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.186111142098068</v>
+        <v>0.4575495920001352</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.049604073904097</v>
+        <v>0.1248857149787443</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>9955</v>
+        <v>9930</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>476.8601329498017</v>
+        <v>476.1365268176141</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>24.85</v>
+        <v>63.1</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>52.11177679053124</v>
+        <v>46.13909481431705</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>21.59338245229573</v>
+        <v>29.72151659261095</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4575495920001352</v>
+        <v>0.7117949515836881</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1248857149787443</v>
+        <v>0.1435948353175619</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>9930</v>
+        <v>8070</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>476.1365268176141</v>
+        <v>475.8057748154141</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>63.1</v>
+        <v>51.4</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.13909481431705</v>
+        <v>55.63552355757272</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>29.72151659261095</v>
+        <v>17.01476940521686</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7117949515836881</v>
+        <v>1.235259528115791</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1435948353175619</v>
+        <v>0.337763642826882</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8070</v>
+        <v>8440</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>475.8057748154141</v>
+        <v>472.7281794917795</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>51.4</v>
+        <v>20.55</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.63552355757272</v>
+        <v>55.78912460366707</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.01476940521686</v>
+        <v>22.43479933477428</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.235259528115791</v>
+        <v>0.6299485194756417</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.337763642826882</v>
+        <v>0.1289581096082066</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8092</v>
+        <v>8064</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>462.4600554495257</v>
+        <v>463.3398046618004</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>13.15</v>
+        <v>103</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>48.5410684939558</v>
+        <v>47.48967361192824</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.72082343695206</v>
+        <v>17.53616990013974</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7585742031113174</v>
+        <v>1.07527190368791</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1345603480737887</v>
+        <v>1.453348279213919</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8227</v>
+        <v>8086</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>443.2037116460196</v>
+        <v>458.5101973463186</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>161</v>
+        <v>117.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.86297982806222</v>
+        <v>48.36628197980028</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.36030476132764</v>
+        <v>22.4258972525593</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.645877602091546</v>
+        <v>0.7491937018888551</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>2.506703657953915</v>
+        <v>1.100350583472466</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>9136</v>
+        <v>8071</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>435.2655196967184</v>
+        <v>455.6822717791341</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>11.7</v>
+        <v>24.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.37143003499804</v>
+        <v>52.22463474091749</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>10.40744770423163</v>
+        <v>14.42308677430792</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6693593677246215</v>
+        <v>0.5322419513436029</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.0679912262908187</v>
+        <v>0.1856795159377095</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8440</v>
+        <v>9136</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>432.7281794917795</v>
+        <v>435.2655196967184</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>20.55</v>
+        <v>11.7</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.78912460366707</v>
+        <v>51.37143003499804</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>22.43479933477428</v>
+        <v>10.40744770423163</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.6299485194756417</v>
+        <v>0.6693593677246215</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.1289581096082066</v>
+        <v>0.0679912262908187</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8249</v>
+        <v>8092</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>432.3826953639392</v>
+        <v>432.4600554495257</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>41.5</v>
+        <v>13.15</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.2910018417936</v>
+        <v>48.5410684939558</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.71501130797508</v>
+        <v>20.72082343695206</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.9466464428856448</v>
+        <v>0.7585742031113174</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.2781614468480149</v>
+        <v>0.1345603480737887</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8102</v>
+        <v>8249</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>430.227982492739</v>
+        <v>432.3826953639392</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>67.5</v>
+        <v>41.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>51.05330926162896</v>
+        <v>46.2910018417936</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>10.4038486796061</v>
+        <v>23.71501130797508</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.1226622035269554</v>
+        <v>0.9466464428856448</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.2801587225198463</v>
+        <v>0.2781614468480149</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8222</v>
+        <v>8147</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>425.376147793611</v>
+        <v>431.7972607066613</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>38.9</v>
+        <v>124</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.64461748480106</v>
+        <v>48.19304635130526</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.63351840447356</v>
+        <v>25.68951432347602</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.391836561260074</v>
+        <v>0.7774721687999316</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0364400409835675</v>
+        <v>1.093632752530516</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8429</v>
+        <v>8102</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>424.4985536354096</v>
+        <v>430.227982492739</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6.01</v>
+        <v>67.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.27957609638885</v>
+        <v>51.05330926162896</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9.459947474331443</v>
+        <v>10.4038486796061</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6421301603580336</v>
+        <v>0.1226622035269554</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.01005847861335</v>
+        <v>0.2801587225198463</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8443</v>
+        <v>8222</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>421.1337850299653</v>
+        <v>425.376147793611</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11.25</v>
+        <v>38.9</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>36.38465672389037</v>
+        <v>49.64461748480106</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>41.75530419497464</v>
+        <v>25.63351840447356</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.287015252781813</v>
+        <v>1.391836561260074</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0159558632793368</v>
+        <v>0.0364400409835675</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8404</v>
+        <v>8429</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>420.1231988233738</v>
+        <v>424.4985536354096</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>16.25</v>
+        <v>6.01</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>46.75043950329373</v>
+        <v>43.27957609638885</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14.2252462686461</v>
+        <v>9.459947474331443</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6738937089338222</v>
+        <v>0.6421301603580336</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0388955212881736</v>
+        <v>0.01005847861335</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8482</v>
+        <v>8443</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>419.2008383893084</v>
+        <v>421.1337850299653</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>47.7</v>
+        <v>11.25</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.22026919423537</v>
+        <v>36.38465672389037</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3.851041046552351</v>
+        <v>41.75530419497464</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.358213258251903</v>
+        <v>0.287015252781813</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0050672804412945</v>
+        <v>-0.0159558632793368</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8086</v>
+        <v>8404</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>418.5101973463186</v>
+        <v>420.1231988233738</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>117.5</v>
+        <v>16.25</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.36628197980028</v>
+        <v>46.75043950329373</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>22.4258972525593</v>
+        <v>14.2252462686461</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7491937018888551</v>
+        <v>0.6738937089338222</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.100350583472466</v>
+        <v>0.0388955212881736</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8240</v>
+        <v>8482</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>416.0376455055229</v>
+        <v>419.2008383893084</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>44.8</v>
+        <v>47.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.89506144442905</v>
+        <v>50.22026919423537</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.74598094227343</v>
+        <v>3.851041046552351</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.594371110257083</v>
+        <v>1.358213258251903</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.7145045700152585</v>
+        <v>-0.0050672804412945</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8071</v>
+        <v>8240</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>415.6822717791341</v>
+        <v>416.0376455055229</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>24.5</v>
+        <v>44.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.22463474091749</v>
+        <v>54.89506144442905</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.42308677430792</v>
+        <v>25.74598094227343</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5322419513436029</v>
+        <v>1.594371110257083</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1856795159377095</v>
+        <v>0.7145045700152585</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>9105</v>
+        <v>8227</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>412.90479348002</v>
+        <v>413.2037116460196</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>8.35</v>
+        <v>161</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.40698646996236</v>
+        <v>52.86297982806222</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15.48584847781395</v>
+        <v>18.36030476132764</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6302401116078229</v>
+        <v>0.645877602091546</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0164873452807053</v>
+        <v>2.506703657953915</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8261</v>
+        <v>9105</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>411.9116592553011</v>
+        <v>412.90479348002</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>187.5</v>
+        <v>8.35</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>46.56438437109063</v>
+        <v>48.40698646996236</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>16.50361183090706</v>
+        <v>15.48584847781395</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.416550959432189</v>
+        <v>0.6302401116078229</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.695340153736435</v>
+        <v>0.0164873452807053</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8464</v>
+        <v>8121</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>410.9134912014217</v>
+        <v>412.5757739810189</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>366.5</v>
+        <v>28.55</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>47.02551196520062</v>
+        <v>40.97527282601633</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.91498724169968</v>
+        <v>28.92004620778427</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7882694408721826</v>
+        <v>0.8004529196264965</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.799318302168852</v>
+        <v>0.4282836220086352</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8111</v>
+        <v>8261</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>401.9214231703433</v>
+        <v>411.9116592553011</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>62.4</v>
+        <v>187.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.82189044109823</v>
+        <v>46.56438437109063</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.5454476004508</v>
+        <v>16.50361183090706</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6118522106575103</v>
+        <v>1.416550959432189</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3985204273748053</v>
+        <v>2.695340153736435</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8045</v>
+        <v>8464</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>400.150450413107</v>
+        <v>410.9134912014217</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>53.2</v>
+        <v>366.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.28582705519808</v>
+        <v>47.02551196520062</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.09958840750623</v>
+        <v>20.91498724169968</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7385276413410768</v>
+        <v>0.7882694408721826</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.350037499707398</v>
+        <v>-1.799318302168852</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8104</v>
+        <v>8109</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>392.9330110216501</v>
+        <v>407.8338964789809</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>31.5</v>
+        <v>130.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>46.00945694864662</v>
+        <v>50.68517557751379</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>25.38397362058426</v>
+        <v>16.96619817811739</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.9073785179289372</v>
+        <v>0.4810904473676982</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.3117951838562334</v>
+        <v>-0.0194607667351514</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8499</v>
+        <v>8045</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>392.6084857295309</v>
+        <v>400.150450413107</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>271</v>
+        <v>53.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.64695815460291</v>
+        <v>47.28582705519808</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.92291162693559</v>
+        <v>14.09958840750623</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.836917441150533</v>
+        <v>0.7385276413410768</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.745386235093792</v>
+        <v>0.350037499707398</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8147</v>
+        <v>8104</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>391.7972607066613</v>
+        <v>392.9330110216501</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>124</v>
+        <v>31.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.19304635130526</v>
+        <v>46.00945694864662</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.68951432347602</v>
+        <v>25.38397362058426</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7774721687999316</v>
+        <v>0.9073785179289372</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.093632752530516</v>
+        <v>0.3117951838562334</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8422</v>
+        <v>8499</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>389.7602426735865</v>
+        <v>392.6084857295309</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>27.1</v>
+        <v>271</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.27055549046003</v>
+        <v>51.64695815460291</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>13.56952754164086</v>
+        <v>14.92291162693559</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.8474869936781482</v>
+        <v>3.836917441150533</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.08745561097681021</v>
+        <v>2.745386235093792</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8080</v>
+        <v>8422</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>373.9083738510026</v>
+        <v>389.7602426735865</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>28</v>
+        <v>27.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.45673140752194</v>
+        <v>54.27055549046003</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>52.76560954830051</v>
+        <v>13.56952754164086</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8125609596685804</v>
+        <v>0.8474869936781482</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0123244625743637</v>
+        <v>0.08745561097681021</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8121</v>
+        <v>8932</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>372.5757739810189</v>
+        <v>385.1700503905222</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>28.55</v>
+        <v>94.3</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>40.97527282601633</v>
+        <v>39.30117549667552</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>28.92004620778427</v>
+        <v>13.49952938915958</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8004529196264965</v>
+        <v>2.261922218506764</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.4282836220086352</v>
+        <v>-0.4219506902806326</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8926</v>
+        <v>8111</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>369.2418346005444</v>
+        <v>371.9214231703433</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>56.8</v>
+        <v>62.4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>38.69312547858893</v>
+        <v>54.82189044109823</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>30.932238668155</v>
+        <v>19.5454476004508</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5788568813467081</v>
+        <v>0.6118522106575103</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4482227638970291</v>
+        <v>0.3985204273748053</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8110</v>
+        <v>8926</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>368.1980553713538</v>
+        <v>369.2418346005444</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>46</v>
+        <v>56.8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.99175645829633</v>
+        <v>38.69312547858893</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>9.866228651315454</v>
+        <v>30.932238668155</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7061173702573003</v>
+        <v>0.5788568813467081</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.3696494334897452</v>
+        <v>0.4482227638970291</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8109</v>
+        <v>8110</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>367.8338964789809</v>
+        <v>368.1980553713538</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>130.5</v>
+        <v>46</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.68517557751379</v>
+        <v>51.99175645829633</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.96619817811739</v>
+        <v>9.866228651315454</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.4810904473676982</v>
+        <v>0.7061173702573003</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.0194607667351514</v>
+        <v>0.3696494334897452</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8481</v>
+        <v>8289</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>361.839347880324</v>
+        <v>365.0631138939091</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>41.2</v>
+        <v>46.35</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>55.31009880712149</v>
+        <v>48.245697573123</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.33478475097821</v>
+        <v>18.52721976460336</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.197371018039711</v>
+        <v>0.6784298967188122</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1034232606627103</v>
+        <v>0.5729448057913278</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8201</v>
+        <v>8481</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>353.0538644423702</v>
+        <v>361.839347880324</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>11.9</v>
+        <v>41.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.77143866879237</v>
+        <v>55.31009880712149</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.12012989206895</v>
+        <v>12.33478475097821</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.299892304013377</v>
+        <v>0.197371018039711</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.047371507072039</v>
+        <v>0.1034232606627103</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8112</v>
+        <v>8201</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>349.435183287089</v>
+        <v>353.0538644423702</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>90.90000000000001</v>
+        <v>11.9</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>49.66301948034295</v>
+        <v>47.77143866879237</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.2758749058418</v>
+        <v>20.12012989206895</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.47216085184195</v>
+        <v>1.299892304013377</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.2637958166129341</v>
+        <v>0.047371507072039</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8374</v>
+        <v>8234</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>346.0726461865015</v>
+        <v>352.248164047337</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.97851672376336</v>
+        <v>51.68276879771057</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>16.36838679175931</v>
+        <v>18.76092435233267</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4595371343834503</v>
+        <v>0.5116699498884609</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0590849115448964</v>
+        <v>-0.0783693473267721</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8081</v>
+        <v>8112</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>345.8567585178446</v>
+        <v>349.435183287089</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>260</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.63794525201446</v>
+        <v>49.66301948034295</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>16.31761830309232</v>
+        <v>12.2758749058418</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5485051840332292</v>
+        <v>0.47216085184195</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.070209476859329</v>
+        <v>-0.2637958166129341</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8932</v>
+        <v>8374</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>345.1700503905222</v>
+        <v>346.0726461865015</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>94.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>39.30117549667552</v>
+        <v>49.97851672376336</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.49952938915958</v>
+        <v>16.36838679175931</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.261922218506764</v>
+        <v>0.4595371343834503</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.4219506902806326</v>
+        <v>0.0590849115448964</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8289</v>
+        <v>8081</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>325.0631138939091</v>
+        <v>345.8567585178446</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>46.35</v>
+        <v>260</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>48.245697573123</v>
+        <v>49.63794525201446</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.52721976460336</v>
+        <v>16.31761830309232</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6784298967188122</v>
+        <v>0.5485051840332292</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.5729448057913278</v>
+        <v>1.070209476859329</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8476</v>
+        <v>8080</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>322.6258853570554</v>
+        <v>343.9083738510026</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>19.9</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.00597295849971</v>
+        <v>51.45673140752194</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>11.63199103327738</v>
+        <v>52.76560954830051</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7474903649016681</v>
+        <v>0.8125609596685804</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0479267900447863</v>
+        <v>0.0123244625743637</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>9110</v>
+        <v>8183</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>319.7758844017502</v>
+        <v>338.8548965242758</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>3.1</v>
+        <v>29.65</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.73005889180092</v>
+        <v>48.24330969818532</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>6.64990059568474</v>
+        <v>20.3903446200394</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.506490107966808</v>
+        <v>0.7992490291360574</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0830707191162364</v>
+        <v>0.08415852397757501</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8101</v>
+        <v>8476</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>316.6453511539835</v>
+        <v>322.6258853570554</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>12.4</v>
+        <v>19.9</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.12102104606424</v>
+        <v>43.00597295849971</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>8.944199604548988</v>
+        <v>11.63199103327738</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.2645351153983523</v>
+        <v>0.7474903649016681</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.3246304680695999</v>
+        <v>0.0479267900447863</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8234</v>
+        <v>9110</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>312.248164047337</v>
+        <v>319.7758844017502</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>68</v>
+        <v>3.1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.68276879771057</v>
+        <v>51.73005889180092</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.76092435233267</v>
+        <v>6.64990059568474</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5116699498884609</v>
+        <v>0.506490107966808</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0783693473267721</v>
+        <v>0.0830707191162364</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8463</v>
+        <v>8076</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>310.933107809466</v>
+        <v>318.8989948003961</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>21.5</v>
+        <v>23.25</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>56.72291130560987</v>
+        <v>45.4766614622364</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>17.65272109793246</v>
+        <v>7.765705764801571</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5005092302243873</v>
+        <v>0.927242813316114</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0587176485514415</v>
+        <v>0.0557769420176847</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8183</v>
+        <v>8101</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>298.8548965242758</v>
+        <v>316.6453511539835</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>29.65</v>
+        <v>12.4</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.24330969818532</v>
+        <v>51.12102104606424</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.3903446200394</v>
+        <v>8.944199604548988</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7992490291360574</v>
+        <v>0.2645351153983523</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.08415852397757501</v>
+        <v>0.3246304680695999</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>9902</v>
+        <v>8463</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>298.6357290999228</v>
+        <v>310.933107809466</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>13.6</v>
+        <v>21.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>44.93355995671451</v>
+        <v>56.72291130560987</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>8.800649991244546</v>
+        <v>17.65272109793246</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.057646849347029</v>
+        <v>0.5005092302243873</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,11 +4545,11 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0077146164293841</v>
+        <v>0.0587176485514415</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>287.1779526627139</v>
+        <v>307.1779526627139</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>24.45</v>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8410</v>
+        <v>9902</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>286.6167334714953</v>
+        <v>298.6357290999228</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>30.5</v>
+        <v>13.6</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>38.21061797999595</v>
+        <v>44.93355995671451</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>22.26521169237453</v>
+        <v>8.800649991244546</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2382106871551852</v>
+        <v>1.057646849347029</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0996335084966169</v>
+        <v>-0.0077146164293841</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>9802</v>
+        <v>8390</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>282.7894927760062</v>
+        <v>298.1311432627424</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>71.7</v>
+        <v>99.8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.60562640678203</v>
+        <v>51.94684347569449</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10.69112895582835</v>
+        <v>15.73638214460221</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4038462947789248</v>
+        <v>0.7733986005243871</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.2003637249161394</v>
+        <v>0.5920776195074637</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8076</v>
+        <v>9802</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>278.8989948003961</v>
+        <v>282.7894927760062</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>23.25</v>
+        <v>71.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.4766614622364</v>
+        <v>47.60562640678203</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7.765705764801571</v>
+        <v>10.69112895582835</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.927242813316114</v>
+        <v>0.4038462947789248</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0557769420176847</v>
+        <v>0.2003637249161394</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>9103</v>
+        <v>8068</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>269.9440760791496</v>
+        <v>280.4484834846212</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>5.08</v>
+        <v>17.05</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.7771468684176</v>
+        <v>40.67537544332563</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.0537142644062</v>
+        <v>13.51912143066086</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5295855790457407</v>
+        <v>0.7394331220603636</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.009073246204712899</v>
+        <v>0.0110821713740467</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8131</v>
+        <v>9103</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>269.2006614636685</v>
+        <v>269.9440760791496</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>62.7</v>
+        <v>5.08</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>46.97646623456652</v>
+        <v>43.7771468684176</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>7.419433536762348</v>
+        <v>11.0537142644062</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6079335757405125</v>
+        <v>0.5295855790457407</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.2923608855500188</v>
+        <v>-0.009073246204712899</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>9904</v>
+        <v>8131</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>264.5091039913911</v>
+        <v>269.2006614636685</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>24.35</v>
+        <v>62.7</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.99115236267824</v>
+        <v>46.97646623456652</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.42101884805333</v>
+        <v>7.419433536762348</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.205746144177928</v>
+        <v>0.6079335757405125</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0431915152399065</v>
+        <v>0.2923608855500188</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8488</v>
+        <v>8059</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>261.9280881202661</v>
+        <v>264.8325375032354</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10</v>
+        <v>13.9</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.91179291380178</v>
+        <v>42.20819473006895</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.21949275833072</v>
+        <v>19.7836643834587</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.1362363350090402</v>
+        <v>0.9932307280114778</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0121638534925729</v>
+        <v>0.08240648068041979</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8411</v>
+        <v>9904</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>260.0967947516219</v>
+        <v>264.5091039913911</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>12.95</v>
+        <v>24.35</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>53.38115655379207</v>
+        <v>45.99115236267824</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.46462542383209</v>
+        <v>19.42101884805333</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3031618294869521</v>
+        <v>1.205746144177928</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0263317978628087</v>
+        <v>0.0431915152399065</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8341</v>
+        <v>8050</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>259.2567896561655</v>
+        <v>263.2064813631319</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>76.7</v>
+        <v>56.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.83350096299573</v>
+        <v>44.62307351138001</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.7411269595829</v>
+        <v>11.22999421900934</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.084434984215798</v>
+        <v>0.2693961994881253</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0910451440759828</v>
+        <v>-0.379537054337907</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8390</v>
+        <v>8488</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>258.1311432627424</v>
+        <v>261.9280881202661</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>99.8</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.94684347569449</v>
+        <v>50.91179291380178</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.73638214460221</v>
+        <v>18.21949275833072</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7733986005243871</v>
+        <v>0.1362363350090402</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.5920776195074637</v>
+        <v>-0.0121638534925729</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8454</v>
+        <v>8097</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>253.400789770245</v>
+        <v>260.9683503068344</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>250</v>
+        <v>49.05</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>42.29666094501501</v>
+        <v>28.94172809166362</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.43662052837788</v>
+        <v>25.41906707033725</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4960576983614056</v>
+        <v>1.036581317635603</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.3220331939957894</v>
+        <v>0.0188658313818725</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8477</v>
+        <v>8411</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>249.6137774489242</v>
+        <v>260.0967947516219</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>15.45</v>
+        <v>12.95</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>49.14544229135476</v>
+        <v>53.38115655379207</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>4.744129656839474</v>
+        <v>14.46462542383209</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.3002377327243102</v>
+        <v>0.3031618294869521</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0205846582288395</v>
+        <v>-0.0263317978628087</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8114</v>
+        <v>8341</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>245.9465628958777</v>
+        <v>259.2567896561655</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>195</v>
+        <v>76.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.78842576348874</v>
+        <v>52.83350096299573</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.73003628992774</v>
+        <v>11.7411269595829</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4187019805029252</v>
+        <v>1.084434984215798</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-1.469599321471017</v>
+        <v>0.0910451440759828</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8068</v>
+        <v>8410</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>240.4484834846212</v>
+        <v>256.6167334714953</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>17.05</v>
+        <v>30.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>40.67537544332563</v>
+        <v>38.21061797999595</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.51912143066086</v>
+        <v>22.26521169237453</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7394331220603636</v>
+        <v>0.2382106871551852</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0110821713740467</v>
+        <v>-0.0996335084966169</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8940</v>
+        <v>8091</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>237.1034079700872</v>
+        <v>255.2157753916384</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>15.15</v>
+        <v>220.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>38.52797774303279</v>
+        <v>43.81658541889351</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.62035520824137</v>
+        <v>14.9075951421026</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.975245236505572</v>
+        <v>0.5736643339597504</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0230952928464726</v>
+        <v>0.4703012776364677</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8059</v>
+        <v>8454</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>224.8325375032355</v>
+        <v>253.400789770245</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>13.9</v>
+        <v>250</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.20819473006895</v>
+        <v>42.29666094501501</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.7836643834587</v>
+        <v>11.43662052837788</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9932307280114778</v>
+        <v>0.4960576983614056</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.08240648068041979</v>
+        <v>-0.3220331939957894</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8050</v>
+        <v>8383</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>223.206481363132</v>
+        <v>251.7646311256282</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>56.4</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.62307351138001</v>
+        <v>44.70365551214903</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>11.22999421900934</v>
+        <v>13.28128710190597</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2693961994881253</v>
+        <v>0.8377401413742578</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.379537054337907</v>
+        <v>-0.3045867920248422</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5509,21 +5509,21 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8097</v>
+        <v>8477</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>220.9683503068344</v>
+        <v>249.6137774489242</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>49.05</v>
+        <v>15.45</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>28.94172809166362</v>
+        <v>49.14544229135476</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>25.41906707033725</v>
+        <v>4.744129656839474</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.036581317635603</v>
+        <v>0.3002377327243102</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0188658313818725</v>
+        <v>-0.0205846582288395</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8091</v>
+        <v>8114</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>215.2157753916384</v>
+        <v>245.9465628958777</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>220.5</v>
+        <v>195</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.81658541889351</v>
+        <v>41.78842576348874</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.9075951421026</v>
+        <v>14.73003628992774</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5736643339597504</v>
+        <v>0.4187019805029252</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.4703012776364677</v>
+        <v>-1.469599321471017</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5615,21 +5615,21 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8383</v>
+        <v>8423</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>211.7646311256282</v>
+        <v>239.5294219576645</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.70365551214903</v>
+        <v>49.46531288669466</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.28128710190597</v>
+        <v>17.29879418738548</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8377401413742578</v>
+        <v>1.168418916176172</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.3045867920248422</v>
+        <v>-0.0046179929742114</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8044</v>
+        <v>8940</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>208.2268261383359</v>
+        <v>237.1034079700872</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>24.4</v>
+        <v>15.15</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>33.4652350316892</v>
+        <v>38.52797774303279</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.73985542213635</v>
+        <v>13.62035520824137</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9002424136611178</v>
+        <v>1.975245236505572</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1482343385507427</v>
+        <v>0.0230952928464726</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8455</v>
+        <v>8044</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>203.8628032094371</v>
+        <v>228.2268261383359</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>10.89500362816788</v>
+        <v>33.4652350316892</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.25945261563091</v>
+        <v>14.73985542213635</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.0015481823371747</v>
+        <v>0.9002424136611178</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.432531609260909</v>
+        <v>-0.1482343385507427</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8423</v>
+        <v>8047</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>199.5294219576645</v>
+        <v>227.6059744411997</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>17.8</v>
+        <v>44</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.46531288669466</v>
+        <v>43.51797461804424</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>17.29879418738548</v>
+        <v>9.436972780240485</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.168418916176172</v>
+        <v>0.2562781745818181</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0046179929742114</v>
+        <v>-0.3590955117073157</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8466</v>
+        <v>8455</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>196.8753968565658</v>
+        <v>223.8628032094371</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>37.54733041050686</v>
+        <v>10.89500362816788</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>27.24543120498111</v>
+        <v>15.25945261563091</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.019908712153769</v>
+        <v>0.0015481823371747</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0471496589042342</v>
+        <v>-1.432531609260909</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8277</v>
+        <v>8088</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>193.1984162231618</v>
+        <v>207.5882092332892</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>8.140000000000001</v>
+        <v>45.75</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.9580764299736</v>
+        <v>41.85895515884366</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.826830787026475</v>
+        <v>13.58343758209626</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.392822576676382</v>
+        <v>0.380398839651127</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0466351654388627</v>
+        <v>0.2289020006305362</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8047</v>
+        <v>8291</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>187.6059744411997</v>
+        <v>206.6982773355024</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>44</v>
+        <v>35.75</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.51797461804424</v>
+        <v>47.55060562929813</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>9.436972780240485</v>
+        <v>12.30969215273276</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2562781745818181</v>
+        <v>0.3571090489235667</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.3590955117073157</v>
+        <v>0.1792838317826992</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8072</v>
+        <v>8466</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>178.5401385744399</v>
+        <v>196.8753968565658</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>26.2</v>
+        <v>15.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.46010786159694</v>
+        <v>37.54733041050686</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.04184195759062</v>
+        <v>27.24543120498111</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.200916113631522</v>
+        <v>1.019908712153769</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.059015407556645</v>
+        <v>-0.0471496589042342</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8088</v>
+        <v>8072</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>167.5882092332892</v>
+        <v>178.5401385744399</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>45.75</v>
+        <v>26.2</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.85895515884366</v>
+        <v>43.46010786159694</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.58343758209626</v>
+        <v>19.04184195759062</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.380398839651127</v>
+        <v>1.200916113631522</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.2289020006305362</v>
+        <v>0.059015407556645</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8291</v>
+        <v>8472</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>166.6982773355024</v>
+        <v>165.107154130495</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>35.75</v>
+        <v>65.7</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.55060562929813</v>
+        <v>33.99492092259649</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.30969215273276</v>
+        <v>17.22152591191638</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3571090489235667</v>
+        <v>1.117458716199917</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1792838317826992</v>
+        <v>0.0399684010048533</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8478</v>
+        <v>8087</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>149.1209667446585</v>
+        <v>163.7995802187797</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>141.5</v>
+        <v>26.1</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>39.86605207119235</v>
+        <v>49.23366240885399</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.34218468765116</v>
+        <v>7.442532682370188</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.8449057976917083</v>
+        <v>0.0514857942112805</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1843121826923046</v>
+        <v>0.0461019516817143</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8069</v>
+        <v>8277</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>146.5043459547673</v>
+        <v>163.1984162231618</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>160.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>38.06149222540301</v>
+        <v>48.9580764299736</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.56615933442729</v>
+        <v>9.826830787026475</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.52749184463082</v>
+        <v>1.392822576676382</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0901316805148599</v>
+        <v>0.0466351654388627</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8067</v>
+        <v>8478</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>145.4913764042074</v>
+        <v>149.1209667446585</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>12.3</v>
+        <v>141.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.81140658262501</v>
+        <v>39.86605207119235</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>8.236485481375427</v>
+        <v>12.34218468765116</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7491376404207429</v>
+        <v>0.8449057976917083</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0709777697038179</v>
+        <v>0.1843121826923046</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8487</v>
+        <v>8067</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>145.2077589963297</v>
+        <v>145.4913764042074</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>40.51912516072922</v>
+        <v>42.81140658262501</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.48270247015094</v>
+        <v>8.236485481375427</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4914339985632009</v>
+        <v>0.7491376404207429</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1680605367960981</v>
+        <v>-0.0709777697038179</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8472</v>
+        <v>8487</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>145.107154130495</v>
+        <v>145.2077589963297</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>65.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>33.99492092259649</v>
+        <v>40.51912516072922</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17.22152591191638</v>
+        <v>14.48270247015094</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.117458716199917</v>
+        <v>0.4914339985632009</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0399684010048533</v>
+        <v>0.1680605367960981</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8087</v>
+        <v>8176</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>123.7995802187796</v>
+        <v>137.866632728196</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>26.1</v>
+        <v>9.81</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>49.23366240885399</v>
+        <v>43.72309341176243</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.442532682370188</v>
+        <v>17.55065898907922</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.0514857942112805</v>
+        <v>0.32393378350222</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0461019516817143</v>
+        <v>-0.0116230971988206</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8089</v>
+        <v>8048</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>121.6864438811206</v>
+        <v>134.7335334069331</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>17.95</v>
+        <v>51.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.06215656359527</v>
+        <v>43.11415786617395</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.355367319494835</v>
+        <v>13.64254169834261</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.11229491846476</v>
+        <v>0.5122234962924279</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0729190164303973</v>
+        <v>0.3108742476852033</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8176</v>
+        <v>8084</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>97.86663272819597</v>
+        <v>131.1400459574824</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>9.81</v>
+        <v>46</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.72309341176243</v>
+        <v>44.83602645694072</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>17.55065898907922</v>
+        <v>17.98345528502759</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.32393378350222</v>
+        <v>0.5140045957482413</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0116230971988206</v>
+        <v>-0.4544806069317083</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>8048</v>
+        <v>8069</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>94.73353340693316</v>
+        <v>116.5043459547673</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>51.8</v>
+        <v>160.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>43.11415786617395</v>
+        <v>38.06149222540301</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.64254169834261</v>
+        <v>18.56615933442729</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5122234962924279</v>
+        <v>0.52749184463082</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.3108742476852033</v>
+        <v>-0.0901316805148599</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>8084</v>
+        <v>8089</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>91.1400459574824</v>
+        <v>91.6864438811206</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>46</v>
+        <v>17.95</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>44.83602645694072</v>
+        <v>44.06215656359527</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>17.98345528502759</v>
+        <v>8.355367319494835</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5140045957482413</v>
+        <v>1.11229491846476</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.4544806069317083</v>
+        <v>0.0729190164303973</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
